--- a/data/trans_dic/P32D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,3</t>
+          <t>4,23; 10,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,38</t>
+          <t>1,5; 8,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,38</t>
+          <t>3,72; 8,32</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,59</t>
+          <t>3,64; 10,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 15,17</t>
+          <t>4,82; 14,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,22</t>
+          <t>4,82; 10,08</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 19,68</t>
+          <t>9,38; 20,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 13,8</t>
+          <t>1,5; 13,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,91</t>
+          <t>8,88; 17,94</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,19</t>
+          <t>5,49; 10,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,92</t>
+          <t>0,58; 5,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,47</t>
+          <t>2,65; 7,62</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 20,66</t>
+          <t>10,0; 21,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 10,91</t>
+          <t>3,27; 11,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 15,86</t>
+          <t>8,44; 15,76</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 18,86</t>
+          <t>2,14; 20,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 17,95</t>
+          <t>4,57; 17,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 15,26</t>
+          <t>4,58; 14,3</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 10,71</t>
+          <t>7,6; 10,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,03</t>
+          <t>2,46; 7,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,94</t>
+          <t>5,88; 8,97</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11565; 29065</t>
+          <t>11929; 29328</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2394; 13532</t>
+          <t>2421; 14216</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16831; 37191</t>
+          <t>16519; 36928</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7851; 22472</t>
+          <t>7730; 21745</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6552; 20312</t>
+          <t>6457; 19162</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16913; 35382</t>
+          <t>16687; 34878</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19064; 41393</t>
+          <t>19740; 42180</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>712; 5480</t>
+          <t>596; 5362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22155; 44792</t>
+          <t>22204; 44878</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27179; 51978</t>
+          <t>27974; 52535</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2232; 24533</t>
+          <t>2408; 24691</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21966; 69095</t>
+          <t>24461; 70475</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22112; 46923</t>
+          <t>22724; 49551</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4517; 14118</t>
+          <t>4232; 14332</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28337; 56536</t>
+          <t>30084; 56202</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1924; 17688</t>
+          <t>2011; 19210</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6105; 21778</t>
+          <t>5546; 21438</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10720; 32823</t>
+          <t>9854; 30756</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>118037; 164526</t>
+          <t>116736; 167145</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27618; 70326</t>
+          <t>24647; 71148</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>146203; 226718</t>
+          <t>149150; 227462</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,39</t>
+          <t>4,05; 10,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,81</t>
+          <t>1,5; 7,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,32</t>
+          <t>3,78; 8,4</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,25</t>
+          <t>3,84; 10,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 14,31</t>
+          <t>5,11; 15,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,08</t>
+          <t>5,34; 10,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 20,05</t>
+          <t>9,48; 19,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,5</t>
+          <t>2,92; 17,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,88; 17,94</t>
+          <t>8,89; 18,1</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,3</t>
+          <t>5,61; 10,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,95</t>
+          <t>3,85; 9,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,62</t>
+          <t>5,74; 9,48</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,0; 21,81</t>
+          <t>11,69; 23,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 11,08</t>
+          <t>3,04; 9,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 15,76</t>
+          <t>9,33; 17,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,48</t>
+          <t>1,97; 21,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 17,67</t>
+          <t>5,14; 19,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 14,3</t>
+          <t>5,01; 15,5</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,88</t>
+          <t>8,16; 11,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,11</t>
+          <t>5,49; 9,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 8,97</t>
+          <t>7,44; 9,94</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>20435</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25428</t>
+          <t>26912</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11929; 29328</t>
+          <t>12282; 30989</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2421; 14216</t>
+          <t>2614; 13584</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16519; 36928</t>
+          <t>18032; 40073</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>15329</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>28706</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7730; 21745</t>
+          <t>8582; 24185</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6457; 19162</t>
+          <t>7444; 22249</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16687; 34878</t>
+          <t>19713; 40233</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>35514</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19740; 42180</t>
+          <t>21531; 45178</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>596; 5362</t>
+          <t>1339; 7886</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22204; 44878</t>
+          <t>24254; 49417</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>41813</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49284</t>
+          <t>56653</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27974; 52535</t>
+          <t>30502; 55126</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2408; 24691</t>
+          <t>8880; 22885</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24461; 70475</t>
+          <t>44429; 73431</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33076</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41165</t>
+          <t>50519</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22724; 49551</t>
+          <t>29579; 58724</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4232; 14332</t>
+          <t>4607; 13975</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30084; 56202</t>
+          <t>37749; 69448</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>19634</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2011; 19210</t>
+          <t>1673; 17908</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5546; 21438</t>
+          <t>6495; 24793</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9854; 30756</t>
+          <t>10587; 32745</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>140510</t>
+          <t>157699</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>60240</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191337</t>
+          <t>217939</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>116736; 167145</t>
+          <t>133444; 187123</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24647; 71148</t>
+          <t>48015; 79187</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>149150; 227462</t>
+          <t>186832; 249417</t>
         </is>
       </c>
     </row>
